--- a/data/trans_orig/IP3103-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP3103-Clase-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3327</t>
+          <t>3705</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3076</t>
+          <t>3283</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4285</t>
+          <t>4459</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13930</t>
+          <t>14413</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1343</t>
+          <t>1470</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7909</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7906</t>
+          <t>7524</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19981</t>
+          <t>19478</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40023</t>
+          <t>39531</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>56953</t>
+          <t>55325</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>38306</t>
+          <t>39018</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>53814</t>
+          <t>53614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>83525</t>
+          <t>83206</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>105405</t>
+          <t>105353</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>56,91%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28529</t>
+          <t>29094</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44222</t>
+          <t>44251</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29575</t>
+          <t>29221</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43972</t>
+          <t>44505</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>63104</t>
+          <t>63671</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84465</t>
+          <t>85014</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,92%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>446</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>4945</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>649</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5696</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1594</t>
+          <t>1562</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7875</t>
+          <t>8484</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2278</t>
+          <t>2255</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>3282</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3608</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6850</t>
+          <t>6825</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17763</t>
+          <t>18254</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3449</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11957</t>
+          <t>12725</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12870</t>
+          <t>12643</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>26084</t>
+          <t>25852</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25207</t>
+          <t>25392</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39070</t>
+          <t>39104</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>33545</t>
+          <t>33561</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>47800</t>
+          <t>47554</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>62697</t>
+          <t>63348</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>83178</t>
+          <t>83492</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>52,12%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26071</t>
+          <t>25565</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40049</t>
+          <t>39138</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22048</t>
+          <t>22569</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35905</t>
+          <t>36269</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51314</t>
+          <t>52048</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>71283</t>
+          <t>71336</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,53%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>857</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6562</t>
+          <t>7193</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7356</t>
+          <t>7135</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2829</t>
+          <t>2768</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11376</t>
+          <t>10551</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>611</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6083</t>
+          <t>6364</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>618</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6056</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9194</t>
+          <t>8783</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5018</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14469</t>
+          <t>14265</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8995</t>
+          <t>8699</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19891</t>
+          <t>20065</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22590</t>
+          <t>22241</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35325</t>
+          <t>34803</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>37728</t>
+          <t>37417</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>53256</t>
+          <t>53366</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>61881</t>
+          <t>64155</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>83101</t>
+          <t>85025</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>53,21%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20004</t>
+          <t>20346</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32675</t>
+          <t>33109</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27552</t>
+          <t>27430</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>42732</t>
+          <t>42523</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>51880</t>
+          <t>51037</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>72561</t>
+          <t>71144</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>44,52%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>1389</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7615</t>
+          <t>7545</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2621</t>
+          <t>2660</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10255</t>
+          <t>10188</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5413</t>
+          <t>5147</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14851</t>
+          <t>14920</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>3470</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>4093</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4625</t>
+          <t>5007</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11192</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22934</t>
+          <t>23471</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9767</t>
+          <t>9384</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>21532</t>
+          <t>22130</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>23998</t>
+          <t>24074</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>40921</t>
+          <t>40264</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>80401</t>
+          <t>79239</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>102177</t>
+          <t>100785</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>83337</t>
+          <t>82274</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>103971</t>
+          <t>104433</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>168090</t>
+          <t>169991</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>199410</t>
+          <t>199179</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>52,82%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>59931</t>
+          <t>60754</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>81848</t>
+          <t>82282</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>59997</t>
+          <t>59732</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>80225</t>
+          <t>82108</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>126973</t>
+          <t>125518</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>156505</t>
+          <t>155489</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>41,24%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6961</t>
+          <t>6973</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>17557</t>
+          <t>17361</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>4295</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>14022</t>
+          <t>13743</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12449</t>
+          <t>13333</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>26911</t>
+          <t>26755</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>4768</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4478</t>
+          <t>4492</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7421</t>
+          <t>7178</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>17369</t>
+          <t>17236</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>9180</t>
+          <t>8722</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>20430</t>
+          <t>20013</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>18630</t>
+          <t>18355</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>33256</t>
+          <t>33539</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>41588</t>
+          <t>42079</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>57851</t>
+          <t>57514</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>47420</t>
+          <t>46285</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>64352</t>
+          <t>64496</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>94020</t>
+          <t>94076</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>117061</t>
+          <t>118450</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>54,28%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>26082</t>
+          <t>26242</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>41787</t>
+          <t>40726</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>33710</t>
+          <t>33596</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>50330</t>
+          <t>50291</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>63969</t>
+          <t>63599</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>85774</t>
+          <t>86546</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,66%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>1987</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>8659</t>
+          <t>8538</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3613</t>
+          <t>3448</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12983</t>
+          <t>11961</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6815</t>
+          <t>6664</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>17900</t>
+          <t>17566</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3398</t>
+          <t>2657</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3066</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3757</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13298</t>
+          <t>12776</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>3151</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>10699</t>
+          <t>11238</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>8761</t>
+          <t>8740</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>20750</t>
+          <t>20167</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,63%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>23614</t>
+          <t>23556</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>36946</t>
+          <t>37288</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>29059</t>
+          <t>27998</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>42379</t>
+          <t>41572</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>56099</t>
+          <t>55526</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>75536</t>
+          <t>73867</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>53,6%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>26613</t>
+          <t>26362</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>40618</t>
+          <t>40461</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>17032</t>
+          <t>17063</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>29226</t>
+          <t>29482</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>46932</t>
+          <t>48074</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>65586</t>
+          <t>66049</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,93%</t>
         </is>
       </c>
     </row>
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>486</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4866</t>
+          <t>4682</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>486</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5623</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>640</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>5893</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>9514</t>
+          <t>9169</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>3648</t>
+          <t>3614</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>12498</t>
+          <t>12357</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>49494</t>
+          <t>49365</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>73416</t>
+          <t>73087</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>45051</t>
+          <t>43759</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>68221</t>
+          <t>66299</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>99590</t>
+          <t>100452</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>132658</t>
+          <t>132986</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>261146</t>
+          <t>260464</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>301294</t>
+          <t>298988</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>293662</t>
+          <t>296831</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>335290</t>
+          <t>335256</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>565450</t>
+          <t>566547</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>624045</t>
+          <t>624442</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,43%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>212988</t>
+          <t>215138</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>250165</t>
+          <t>252468</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>217990</t>
+          <t>216636</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>257867</t>
+          <t>255682</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>440327</t>
+          <t>439449</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>497319</t>
+          <t>496816</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,12%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>16778</t>
+          <t>17419</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>32304</t>
+          <t>31919</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>20975</t>
+          <t>19875</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>37485</t>
+          <t>36476</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>42603</t>
+          <t>41936</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>63953</t>
+          <t>64234</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3972</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3962</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5966</t>
+          <t>5750</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15945</t>
+          <t>16100</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11112</t>
+          <t>10603</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10543</t>
+          <t>10539</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23582</t>
+          <t>22797</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35244</t>
+          <t>35382</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50858</t>
+          <t>50341</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27300</t>
+          <t>27408</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>41384</t>
+          <t>41483</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>68489</t>
+          <t>67666</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>88110</t>
+          <t>87564</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,46%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13616</t>
+          <t>14164</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27240</t>
+          <t>27577</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25157</t>
+          <t>25654</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39305</t>
+          <t>40041</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42624</t>
+          <t>42871</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61970</t>
+          <t>61863</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,77%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6960</t>
+          <t>6744</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16970</t>
+          <t>17382</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6232,7 +6232,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11190</t>
+          <t>10579</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11382</t>
+          <t>11438</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24075</t>
+          <t>24146</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,74%</t>
         </is>
       </c>
     </row>
@@ -6427,7 +6427,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>3328</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3424</t>
+          <t>3398</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>4299</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5333</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15178</t>
+          <t>15594</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>5573</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15791</t>
+          <t>15422</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13556</t>
+          <t>13437</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28377</t>
+          <t>28038</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32116</t>
+          <t>31980</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>46339</t>
+          <t>46417</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28431</t>
+          <t>28578</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>43990</t>
+          <t>43500</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>64861</t>
+          <t>64219</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>85566</t>
+          <t>86882</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>49,45%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22616</t>
+          <t>21499</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37064</t>
+          <t>35961</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19544</t>
+          <t>18846</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33210</t>
+          <t>33540</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44852</t>
+          <t>44760</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65242</t>
+          <t>65410</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,23%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3606</t>
+          <t>3560</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12277</t>
+          <t>12356</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>11769</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24949</t>
+          <t>24319</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17850</t>
+          <t>17780</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32934</t>
+          <t>32610</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,56%</t>
         </is>
       </c>
     </row>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3279</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3654</t>
+          <t>3493</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7931</t>
+          <t>7549</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18151</t>
+          <t>18546</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4678</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13977</t>
+          <t>13987</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14549</t>
+          <t>14504</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28383</t>
+          <t>27685</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>34408</t>
+          <t>34076</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>48097</t>
+          <t>48814</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27701</t>
+          <t>28091</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>43143</t>
+          <t>43164</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>67439</t>
+          <t>67189</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>87614</t>
+          <t>87403</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,67%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12288</t>
+          <t>12509</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23723</t>
+          <t>24966</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18250</t>
+          <t>18070</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31595</t>
+          <t>31892</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33323</t>
+          <t>33321</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>51652</t>
+          <t>51628</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,29%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3953</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12204</t>
+          <t>12333</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7417</t>
+          <t>7966</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17803</t>
+          <t>17740</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13516</t>
+          <t>14009</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>27199</t>
+          <t>27637</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,29%</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4488</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>3823</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>695</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6665</t>
+          <t>6318</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>21652</t>
+          <t>21178</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>37484</t>
+          <t>38395</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>31721</t>
+          <t>31626</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>52777</t>
+          <t>50863</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>57868</t>
+          <t>58475</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>82892</t>
+          <t>83244</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,29%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>74447</t>
+          <t>74538</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>96113</t>
+          <t>96595</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>86634</t>
+          <t>85531</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>109958</t>
+          <t>112061</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>165877</t>
+          <t>166878</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>199264</t>
+          <t>201191</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>51,46%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>42205</t>
+          <t>42041</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>62306</t>
+          <t>62697</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>40264</t>
+          <t>40668</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>60022</t>
+          <t>61034</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>89337</t>
+          <t>88060</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>117313</t>
+          <t>115141</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,45%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10803</t>
+          <t>10614</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>22380</t>
+          <t>23344</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12052</t>
+          <t>11501</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25297</t>
+          <t>24525</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>26101</t>
+          <t>25262</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>43907</t>
+          <t>43495</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -8508,7 +8508,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t>4127</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3471</t>
+          <t>3804</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>16417</t>
+          <t>16261</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>31490</t>
+          <t>31307</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>16752</t>
+          <t>17434</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>31717</t>
+          <t>32775</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>37438</t>
+          <t>37827</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>58775</t>
+          <t>60208</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,49%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>47119</t>
+          <t>45705</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>65482</t>
+          <t>65408</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>42937</t>
+          <t>42966</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>60836</t>
+          <t>61144</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>93571</t>
+          <t>93942</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>121277</t>
+          <t>121511</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,4%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>30735</t>
+          <t>31145</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>48083</t>
+          <t>47871</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>30071</t>
+          <t>29606</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>47140</t>
+          <t>46922</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>65663</t>
+          <t>62710</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>90636</t>
+          <t>88375</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,02%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>13769</t>
+          <t>14073</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>27743</t>
+          <t>28585</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>9925</t>
+          <t>10031</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>22147</t>
+          <t>22257</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>26802</t>
+          <t>27757</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>44113</t>
+          <t>45636</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>17,05%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2312</t>
+          <t>2155</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>9485</t>
+          <t>9726</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7881</t>
+          <t>8026</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>18086</t>
+          <t>18261</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>11936</t>
+          <t>11606</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>24485</t>
+          <t>24721</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>19939</t>
+          <t>19120</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>31401</t>
+          <t>31359</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>24457</t>
+          <t>24349</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>38308</t>
+          <t>37969</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>47079</t>
+          <t>48224</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>65414</t>
+          <t>66356</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>57,23%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>11415</t>
+          <t>10980</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>22231</t>
+          <t>21901</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>12771</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>25014</t>
+          <t>25501</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>27620</t>
+          <t>27003</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>43408</t>
+          <t>43226</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,28%</t>
         </is>
       </c>
     </row>
@@ -9607,7 +9607,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5365</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>9470</t>
+          <t>9584</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>3078</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>12634</t>
+          <t>11397</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>693</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>6967</t>
+          <t>6498</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>7417</t>
+          <t>7489</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2764</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>11385</t>
+          <t>11674</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>75006</t>
+          <t>76549</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>104441</t>
+          <t>105281</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>86996</t>
+          <t>85918</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>117502</t>
+          <t>114993</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>170937</t>
+          <t>170340</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>211156</t>
+          <t>213836</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,79%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>269685</t>
+          <t>266851</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>310750</t>
+          <t>309245</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>266383</t>
+          <t>266824</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>309706</t>
+          <t>308129</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>548554</t>
+          <t>547097</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>605477</t>
+          <t>605543</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>156642</t>
+          <t>156963</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>191810</t>
+          <t>193847</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>169497</t>
+          <t>168462</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>205847</t>
+          <t>209432</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>336123</t>
+          <t>336920</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>389058</t>
+          <t>387980</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,45%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>52905</t>
+          <t>52072</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>77675</t>
+          <t>76815</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>60263</t>
+          <t>61057</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>87196</t>
+          <t>87193</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>118945</t>
+          <t>119439</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>156210</t>
+          <t>155153</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -10753,7 +10753,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10768,7 +10768,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10823,7 +10823,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3552</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>4423</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14845</t>
+          <t>15060</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3499</t>
+          <t>3132</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11792</t>
+          <t>12074</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9478</t>
+          <t>9930</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22646</t>
+          <t>23837</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25207</t>
+          <t>24802</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38928</t>
+          <t>38513</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25569</t>
+          <t>25054</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>40149</t>
+          <t>40288</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>54066</t>
+          <t>54314</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>75015</t>
+          <t>75692</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>46,22%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16280</t>
+          <t>15999</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27932</t>
+          <t>28351</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19460</t>
+          <t>18635</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33766</t>
+          <t>33412</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38255</t>
+          <t>38495</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56867</t>
+          <t>57146</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,9%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7250</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17129</t>
+          <t>17877</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17384</t>
+          <t>17721</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30949</t>
+          <t>31711</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>27430</t>
+          <t>27921</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>43917</t>
+          <t>45545</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>27,81%</t>
         </is>
       </c>
     </row>
@@ -11470,7 +11470,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3092</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3663</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11520,7 +11520,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7689</t>
+          <t>7947</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18446</t>
+          <t>18376</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6908</t>
+          <t>6887</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17177</t>
+          <t>16780</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17752</t>
+          <t>16944</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32031</t>
+          <t>30653</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,23%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28619</t>
+          <t>28847</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43976</t>
+          <t>44123</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>37780</t>
+          <t>37153</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>53879</t>
+          <t>54410</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>68839</t>
+          <t>71101</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>92545</t>
+          <t>93205</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>46,3%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17647</t>
+          <t>17757</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30748</t>
+          <t>30960</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23513</t>
+          <t>22958</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39282</t>
+          <t>39055</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44932</t>
+          <t>43772</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65374</t>
+          <t>64181</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>31,88%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17849</t>
+          <t>17844</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31961</t>
+          <t>31239</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11948</t>
+          <t>11902</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23714</t>
+          <t>23958</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32584</t>
+          <t>31991</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>50853</t>
+          <t>50389</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,03%</t>
         </is>
       </c>
     </row>
@@ -12152,7 +12152,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>4394</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12187,7 +12187,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4508</t>
+          <t>3180</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4986</t>
+          <t>4792</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14343</t>
+          <t>13680</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2906</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11313</t>
+          <t>11558</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9879</t>
+          <t>9863</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21651</t>
+          <t>21550</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,91%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17063</t>
+          <t>17130</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>28721</t>
+          <t>28429</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19386</t>
+          <t>19001</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>32141</t>
+          <t>32483</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>39431</t>
+          <t>39859</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>57008</t>
+          <t>57540</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>45,16%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8404</t>
+          <t>8136</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18419</t>
+          <t>18150</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17625</t>
+          <t>17919</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30768</t>
+          <t>30646</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28912</t>
+          <t>29545</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>45656</t>
+          <t>45578</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,77%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8342</t>
+          <t>8528</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18796</t>
+          <t>18432</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8746</t>
+          <t>8884</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18902</t>
+          <t>19412</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20041</t>
+          <t>20194</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>33722</t>
+          <t>34221</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,86%</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4282</t>
+          <t>3986</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12869,7 +12869,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4424</t>
+          <t>4081</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>16602</t>
+          <t>17354</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>32200</t>
+          <t>32579</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13596</t>
+          <t>13054</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>27066</t>
+          <t>26906</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>33091</t>
+          <t>32819</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>54390</t>
+          <t>53922</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,18%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>68020</t>
+          <t>66797</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>89250</t>
+          <t>89194</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>65226</t>
+          <t>65263</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>87592</t>
+          <t>87753</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>137632</t>
+          <t>139949</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>170555</t>
+          <t>171220</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,85%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>40146</t>
+          <t>41504</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>62330</t>
+          <t>61247</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>40124</t>
+          <t>40960</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>60200</t>
+          <t>59993</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>87676</t>
+          <t>87440</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>115649</t>
+          <t>115998</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,35%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>44549</t>
+          <t>44095</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>64673</t>
+          <t>63670</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>46324</t>
+          <t>46790</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>66687</t>
+          <t>67051</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>95116</t>
+          <t>95905</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>124118</t>
+          <t>125403</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,65%</t>
         </is>
       </c>
     </row>
@@ -13481,7 +13481,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4205</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13496,7 +13496,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13516,7 +13516,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4977</t>
+          <t>4964</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13531,7 +13531,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>688</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5848</t>
+          <t>5172</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13566,7 +13566,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8486</t>
+          <t>8646</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>20455</t>
+          <t>20570</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>9346</t>
+          <t>9290</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>21255</t>
+          <t>21886</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>21723</t>
+          <t>20610</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>38471</t>
+          <t>37356</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,06%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>36629</t>
+          <t>37184</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>54387</t>
+          <t>54253</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>31041</t>
+          <t>30602</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>48837</t>
+          <t>48922</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>73489</t>
+          <t>73631</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>98524</t>
+          <t>98436</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,05%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>26364</t>
+          <t>26767</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>43420</t>
+          <t>43103</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>26909</t>
+          <t>26716</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>44151</t>
+          <t>43659</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>59507</t>
+          <t>57873</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>82297</t>
+          <t>81229</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,57%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>29188</t>
+          <t>28309</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>45917</t>
+          <t>45127</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>34229</t>
+          <t>34554</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>52132</t>
+          <t>53172</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>67019</t>
+          <t>67921</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>91696</t>
+          <t>91044</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,26%</t>
         </is>
       </c>
     </row>
@@ -14163,7 +14163,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3238</t>
+          <t>3806</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3892</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14213,7 +14213,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14233,7 +14233,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>4795</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14248,7 +14248,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>3057</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>11182</t>
+          <t>11870</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>5118</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>14723</t>
+          <t>14381</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>10591</t>
+          <t>10291</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>22310</t>
+          <t>22642</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,59%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>15216</t>
+          <t>15425</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>27036</t>
+          <t>27872</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>14509</t>
+          <t>14503</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>27080</t>
+          <t>27014</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>34438</t>
+          <t>33553</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>50786</t>
+          <t>51032</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>41,89%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>13739</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>26388</t>
+          <t>26058</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>9737</t>
+          <t>10028</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>20994</t>
+          <t>20447</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>26692</t>
+          <t>27406</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>43025</t>
+          <t>42976</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,28%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>5138</t>
+          <t>5388</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>13872</t>
+          <t>14437</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>13484</t>
+          <t>13762</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>26024</t>
+          <t>26323</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>20920</t>
+          <t>21325</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>35430</t>
+          <t>37047</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>30,41%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>759</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7273</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>8173</t>
+          <t>7693</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14895,7 +14895,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>3562</t>
+          <t>3429</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>12146</t>
+          <t>12548</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>60110</t>
+          <t>60314</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>86723</t>
+          <t>87852</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>55941</t>
+          <t>55475</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>82926</t>
+          <t>81516</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>122153</t>
+          <t>122270</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>161227</t>
+          <t>159689</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15043,7 +15043,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>215503</t>
+          <t>216915</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>255429</t>
+          <t>258015</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>219282</t>
+          <t>219363</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>259533</t>
+          <t>259943</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>445941</t>
+          <t>448518</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>502986</t>
+          <t>503831</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>39,08%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>147108</t>
+          <t>147989</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>182478</t>
+          <t>182165</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>162955</t>
+          <t>162049</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>200235</t>
+          <t>202221</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>318662</t>
+          <t>317459</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>371475</t>
+          <t>371001</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,78%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>131551</t>
+          <t>131520</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>165010</t>
+          <t>166686</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15312,7 +15312,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>156101</t>
+          <t>153846</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>190600</t>
+          <t>193081</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>296701</t>
+          <t>300235</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>346654</t>
+          <t>347967</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,99%</t>
         </is>
       </c>
     </row>
